--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/CharaText.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/CharaText.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1461" uniqueCount="1142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="1156">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -1044,9 +1044,9 @@
 「보물을 썩히고 있는 게 아닌가」</t>
   </si>
   <si>
-    <t xml:space="preserve">You hear the rhythmic clang of a hammer on steel
-You hear the whoosh of a bellows being pumped
-You hear the perfect ring of steel-on-steel. It makes your blood race
+    <t xml:space="preserve">You hear the rhythmic clang of a hammer on steel.
+You hear the whoosh of a bellows being pumped.
+You hear the perfect ring of steel-on-steel. It makes your blood race.
 "And just what shall you be, oh noble ingot? &amp;A dagger perhaps, an axe blade by chance? &amp;Let us find out..."
 "Ah! A good shipment of steel today. &amp;Oh, what to make, decisions, decisions..."
 "With this, I have created half a legend. &amp;Your wielder will make the other half with you."
@@ -1830,7 +1830,7 @@
 「이놈잇!」</t>
   </si>
   <si>
-    <t xml:space="preserve">"Atone for you sin."
+    <t xml:space="preserve">"Atone for your sin."
 "Well, you need to be punished."
 "You sonova..."
 "Shit!"</t>
@@ -1842,7 +1842,7 @@
 「くそがーっ」</t>
   </si>
   <si>
-    <t xml:space="preserve">「아아, 신이시여-」</t>
+    <t xml:space="preserve">「아아, 신이시여—」</t>
   </si>
   <si>
     <t xml:space="preserve">"God help me!"</t>
@@ -1858,6 +1858,72 @@
   </si>
   <si>
     <t xml:space="preserve">「地獄に墜ちなさい♪」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nurse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">너스 냄새가 난다…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You catch the faint scent of a nurse...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ナースの匂いがする…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「이건… 중증이네요♪」
+「가만히 계세요!」
+「조금 따끔해요」
+「장난 그만!」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"This looks... serious♪"
+"Please, don't struggle!"
+"This may hurt a little."
+"Now, no misbehaving!"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「これは…重症ですね♪」
+「暴れないでください！」
+「少し痛みますよ」
+「おいたはダメ！」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「꺄아—」
+「아직… 근무시간인데…」
+「아무나… 구급상자 좀…」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Eek!"
+"But...I'm still on duty..."
+"Someone...get the first-aid kit..."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「キャァー」
+「まだ…勤務時間なのに…」
+「誰か…救急箱を…」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「다음 환자분, 오세요♪」
+「이제 안 아플 거예요」
+「네, 푹 쉬세요」
+「수술 성공입니다」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Next patient, please♪"
+"You won't feel any more pain."
+"Now, please get some rest."
+"The operation was a success."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「次の患者さん、どうぞ♪」
+「もう痛くないですよ」
+「はい、ご安静に」
+「手術は成功しました」</t>
   </si>
   <si>
     <t xml:space="preserve">punk</t>
@@ -1889,9 +1955,9 @@
   <si>
     <t xml:space="preserve">「도망쳐어어」
 「너 없애버리겠어」
-「개자식-」
-「하지 마-」
-「거짓말이야-」
+「개자식—」
+「하지 마—」
+「거짓말이야—」
 「내가 지다니…」</t>
   </si>
   <si>
@@ -5467,7 +5533,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q134"/>
+  <dimension ref="A1:Q135"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="1" style="0" width="16.15"/>
@@ -7021,791 +7087,782 @@
         <v>395</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
         <v>396</v>
       </c>
       <c r="B44" s="0" t="s">
+        <v>397</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>398</v>
+      </c>
+      <c r="D44" s="0" t="s">
+        <v>399</v>
+      </c>
+      <c r="E44" s="0" t="s">
+        <v>400</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="O44" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="Q44" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0" t="s">
+        <v>410</v>
+      </c>
+      <c r="B45" s="0" t="s">
         <v>358</v>
       </c>
-      <c r="I44" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="N44" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="O44" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="Q44" s="2" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
-        <v>405</v>
-      </c>
-      <c r="B45" s="0" t="s">
+      <c r="I45" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="Q45" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="B46" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="I45" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="K45" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="M45" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="N45" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="O45" s="0" t="s">
-        <v>412</v>
-      </c>
-      <c r="P45" s="0" t="s">
-        <v>413</v>
-      </c>
-      <c r="Q45" s="0" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
-        <v>415</v>
-      </c>
-      <c r="B46" s="0" t="s">
-        <v>18</v>
+      <c r="I46" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>422</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="O46" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="P46" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="Q46" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
+      </c>
+      <c r="O46" s="0" t="s">
+        <v>426</v>
+      </c>
+      <c r="P46" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="Q46" s="0" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="B47" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="O47" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="Q47" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="B48" s="0" t="s">
         <v>152</v>
       </c>
-      <c r="C47" s="0" t="s">
-        <v>423</v>
-      </c>
-      <c r="D47" s="0" t="s">
-        <v>424</v>
-      </c>
-      <c r="E47" s="0" t="s">
-        <v>423</v>
-      </c>
-      <c r="L47" s="0" t="s">
-        <v>425</v>
-      </c>
-      <c r="M47" s="0" t="s">
-        <v>426</v>
-      </c>
-      <c r="N47" s="0" t="s">
-        <v>427</v>
-      </c>
-      <c r="O47" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="P47" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="Q47" s="2" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
-        <v>431</v>
-      </c>
-      <c r="B48" s="0" t="s">
-        <v>432</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="M48" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="N48" s="2" t="s">
-        <v>435</v>
+      <c r="C48" s="0" t="s">
+        <v>437</v>
+      </c>
+      <c r="D48" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="E48" s="0" t="s">
+        <v>437</v>
+      </c>
+      <c r="L48" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="M48" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="N48" s="0" t="s">
+        <v>441</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="255.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="B49" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="Q49" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="255.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0" t="s">
+        <v>450</v>
+      </c>
+      <c r="B50" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="J49" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="K49" s="2" t="s">
+      <c r="C50" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="L50" s="0" t="s">
+        <v>457</v>
+      </c>
+      <c r="M50" s="0" t="s">
+        <v>458</v>
+      </c>
+      <c r="N50" s="0" t="s">
+        <v>459</v>
+      </c>
+      <c r="O50" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="L49" s="0" t="s">
+      <c r="P50" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="M49" s="0" t="s">
+      <c r="Q50" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="N49" s="0" t="s">
-        <v>445</v>
-      </c>
-      <c r="O49" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="P49" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="Q49" s="2" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
-        <v>446</v>
-      </c>
-      <c r="B50" s="0" t="s">
+    </row>
+    <row r="51" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0" t="s">
+        <v>460</v>
+      </c>
+      <c r="B51" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="L50" s="0" t="s">
-        <v>453</v>
-      </c>
-      <c r="M50" s="0" t="s">
-        <v>454</v>
-      </c>
-      <c r="N50" s="0" t="s">
-        <v>455</v>
-      </c>
-      <c r="O50" s="0" t="s">
-        <v>456</v>
-      </c>
-      <c r="P50" s="0" t="s">
-        <v>457</v>
-      </c>
-      <c r="Q50" s="0" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
-        <v>459</v>
-      </c>
-      <c r="B51" s="0" t="s">
+      <c r="C51" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="L51" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="M51" s="0" t="s">
+        <v>468</v>
+      </c>
+      <c r="N51" s="0" t="s">
+        <v>469</v>
+      </c>
+      <c r="O51" s="0" t="s">
+        <v>470</v>
+      </c>
+      <c r="P51" s="0" t="s">
+        <v>471</v>
+      </c>
+      <c r="Q51" s="0" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="B52" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="I51" s="0" t="s">
-        <v>463</v>
-      </c>
-      <c r="J51" s="0" t="s">
-        <v>464</v>
-      </c>
-      <c r="K51" s="0" t="s">
-        <v>465</v>
-      </c>
-      <c r="L51" s="0" t="s">
-        <v>466</v>
-      </c>
-      <c r="M51" s="0" t="s">
-        <v>467</v>
-      </c>
-      <c r="N51" s="0" t="s">
-        <v>468</v>
-      </c>
-      <c r="O51" s="0" t="s">
-        <v>466</v>
-      </c>
-      <c r="P51" s="0" t="s">
-        <v>467</v>
-      </c>
-      <c r="Q51" s="0" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
-        <v>469</v>
-      </c>
-      <c r="B52" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="J52" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="L52" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="M52" s="2" t="s">
+      <c r="C52" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="N52" s="2" t="s">
+      <c r="D52" s="2" t="s">
         <v>475</v>
       </c>
+      <c r="E52" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="I52" s="0" t="s">
+        <v>477</v>
+      </c>
+      <c r="J52" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="K52" s="0" t="s">
+        <v>479</v>
+      </c>
+      <c r="L52" s="0" t="s">
+        <v>480</v>
+      </c>
+      <c r="M52" s="0" t="s">
+        <v>481</v>
+      </c>
+      <c r="N52" s="0" t="s">
+        <v>482</v>
+      </c>
       <c r="O52" s="0" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="P52" s="0" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="Q52" s="0" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>480</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="I53" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="I53" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="J53" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="K53" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="L53" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="M53" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="N53" s="0" t="s">
-        <v>484</v>
+      <c r="J53" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>489</v>
       </c>
       <c r="O53" s="0" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="P53" s="0" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="Q53" s="0" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="B54" s="0" t="s">
+        <v>494</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="I54" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="J54" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="K54" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="L54" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="M54" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="N54" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="O54" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="P54" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="Q54" s="0" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0" t="s">
+        <v>499</v>
+      </c>
+      <c r="B55" s="0" t="s">
         <v>273</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="I54" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="J54" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="K54" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="L54" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="M54" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="N54" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="O54" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="P54" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="Q54" s="0" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
-        <v>489</v>
-      </c>
-      <c r="B55" s="0" t="s">
-        <v>490</v>
-      </c>
       <c r="C55" s="2" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="L55" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="M55" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="N55" s="2" t="s">
-        <v>496</v>
+        <v>502</v>
+      </c>
+      <c r="I55" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="J55" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="K55" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="L55" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="M55" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="N55" s="0" t="s">
+        <v>498</v>
       </c>
       <c r="O55" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P55" s="0" t="s">
         <v>498</v>
       </c>
       <c r="Q55" s="0" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>490</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="J56" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="K56" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>507</v>
       </c>
       <c r="L56" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="O56" s="0" t="s">
+        <v>511</v>
+      </c>
+      <c r="P56" s="0" t="s">
+        <v>512</v>
+      </c>
+      <c r="Q56" s="0" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="s">
+        <v>514</v>
+      </c>
+      <c r="B57" s="0" t="s">
         <v>504</v>
       </c>
-      <c r="M56" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="N56" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="O56" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="P56" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="Q56" s="2" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="B57" s="0" t="s">
-        <v>480</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="I57" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="J57" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="K57" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="L57" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="M57" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="N57" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="O57" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="P57" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="Q57" s="0" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I57" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="O57" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="P57" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="Q57" s="2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="B58" s="0" t="s">
+        <v>494</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="I58" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="J58" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="K58" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="L58" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="M58" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="N58" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="O58" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="P58" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="Q58" s="0" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="s">
+        <v>528</v>
+      </c>
+      <c r="B59" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="I58" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="J58" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="K58" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="L58" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="M58" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="N58" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="O58" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="P58" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="Q58" s="0" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
-        <v>518</v>
-      </c>
-      <c r="B59" s="0" t="s">
+      <c r="C59" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="I59" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="J59" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="K59" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="L59" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="M59" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="N59" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="O59" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="P59" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="Q59" s="0" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0" t="s">
+        <v>532</v>
+      </c>
+      <c r="B60" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="J59" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="K59" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="L59" s="0" t="s">
-        <v>525</v>
-      </c>
-      <c r="M59" s="0" t="s">
-        <v>526</v>
-      </c>
-      <c r="N59" s="0" t="s">
-        <v>527</v>
-      </c>
-      <c r="O59" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="P59" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="Q59" s="2" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
-        <v>531</v>
-      </c>
-      <c r="B60" s="0" t="s">
+      <c r="C60" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="L60" s="0" t="s">
+        <v>539</v>
+      </c>
+      <c r="M60" s="0" t="s">
+        <v>540</v>
+      </c>
+      <c r="N60" s="0" t="s">
+        <v>541</v>
+      </c>
+      <c r="O60" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="P60" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="Q60" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="0" t="s">
+        <v>545</v>
+      </c>
+      <c r="B61" s="0" t="s">
         <v>18</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="J60" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="K60" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="L60" s="0" t="s">
-        <v>535</v>
-      </c>
-      <c r="M60" s="0" t="s">
-        <v>536</v>
-      </c>
-      <c r="N60" s="0" t="s">
-        <v>537</v>
-      </c>
-      <c r="O60" s="0" t="s">
-        <v>538</v>
-      </c>
-      <c r="P60" s="0" t="s">
-        <v>539</v>
-      </c>
-      <c r="Q60" s="0" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
-        <v>541</v>
-      </c>
-      <c r="B61" s="0" t="s">
-        <v>542</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>545</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>546</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="L61" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="M61" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="N61" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="O61" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="P61" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="Q61" s="2" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>548</v>
+      </c>
+      <c r="L61" s="0" t="s">
+        <v>549</v>
+      </c>
+      <c r="M61" s="0" t="s">
+        <v>550</v>
+      </c>
+      <c r="N61" s="0" t="s">
+        <v>551</v>
+      </c>
+      <c r="O61" s="0" t="s">
+        <v>552</v>
+      </c>
+      <c r="P61" s="0" t="s">
+        <v>553</v>
+      </c>
+      <c r="Q61" s="0" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>18</v>
+        <v>556</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="I62" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="J62" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="K62" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="L62" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="M62" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="N62" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="O62" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="P62" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q62" s="0" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>559</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="P62" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="Q62" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>551</v>
+        <v>561</v>
       </c>
       <c r="B63" s="0" t="s">
         <v>18</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>552</v>
+        <v>562</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="I63" s="0" t="s">
         <v>241</v>
@@ -7835,223 +7892,232 @@
         <v>241</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="141" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>559</v>
+        <v>18</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>562</v>
+        <v>568</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>571</v>
       </c>
       <c r="I64" s="0" t="s">
         <v>241</v>
       </c>
+      <c r="J64" s="0" t="s">
+        <v>241</v>
+      </c>
       <c r="K64" s="0" t="s">
         <v>241</v>
       </c>
       <c r="L64" s="0" t="s">
         <v>241</v>
       </c>
+      <c r="M64" s="0" t="s">
+        <v>241</v>
+      </c>
       <c r="N64" s="0" t="s">
         <v>241</v>
       </c>
       <c r="O64" s="0" t="s">
         <v>241</v>
       </c>
+      <c r="P64" s="0" t="s">
+        <v>241</v>
+      </c>
       <c r="Q64" s="0" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="141" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="B65" s="0" t="s">
+        <v>573</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="I65" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="K65" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="L65" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="N65" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="O65" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q65" s="0" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="0" t="s">
+        <v>577</v>
+      </c>
+      <c r="B66" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="F65" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="I65" s="0" t="s">
-        <v>567</v>
-      </c>
-      <c r="J65" s="0" t="s">
-        <v>567</v>
-      </c>
-      <c r="K65" s="0" t="s">
-        <v>567</v>
-      </c>
-      <c r="L65" s="0" t="s">
-        <v>567</v>
-      </c>
-      <c r="M65" s="0" t="s">
-        <v>567</v>
-      </c>
-      <c r="N65" s="0" t="s">
-        <v>567</v>
-      </c>
-      <c r="O65" s="0" t="s">
-        <v>567</v>
-      </c>
-      <c r="P65" s="0" t="s">
-        <v>567</v>
-      </c>
-      <c r="Q65" s="0" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
-        <v>568</v>
-      </c>
-      <c r="B66" s="0" t="s">
+      <c r="F66" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="I66" s="0" t="s">
+        <v>581</v>
+      </c>
+      <c r="J66" s="0" t="s">
+        <v>581</v>
+      </c>
+      <c r="K66" s="0" t="s">
+        <v>581</v>
+      </c>
+      <c r="L66" s="0" t="s">
+        <v>581</v>
+      </c>
+      <c r="M66" s="0" t="s">
+        <v>581</v>
+      </c>
+      <c r="N66" s="0" t="s">
+        <v>581</v>
+      </c>
+      <c r="O66" s="0" t="s">
+        <v>581</v>
+      </c>
+      <c r="P66" s="0" t="s">
+        <v>581</v>
+      </c>
+      <c r="Q66" s="0" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="0" t="s">
+        <v>582</v>
+      </c>
+      <c r="B67" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="I66" s="0" t="s">
+      <c r="C67" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="I67" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="J66" s="0" t="s">
+      <c r="J67" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="K66" s="0" t="s">
+      <c r="K67" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="L66" s="0" t="s">
+      <c r="L67" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="M66" s="0" t="s">
+      <c r="M67" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="N66" s="0" t="s">
+      <c r="N67" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="O66" s="0" t="s">
+      <c r="O67" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="P66" s="0" t="s">
+      <c r="P67" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="Q66" s="0" t="s">
+      <c r="Q67" s="0" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
-        <v>575</v>
-      </c>
-      <c r="B67" s="0" t="s">
+    <row r="68" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="0" t="s">
+        <v>589</v>
+      </c>
+      <c r="B68" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="F67" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="I67" s="0" t="s">
-        <v>579</v>
-      </c>
-      <c r="J67" s="0" t="s">
-        <v>579</v>
-      </c>
-      <c r="K67" s="0" t="s">
-        <v>579</v>
-      </c>
-      <c r="L67" s="0" t="s">
-        <v>579</v>
-      </c>
-      <c r="M67" s="0" t="s">
-        <v>579</v>
-      </c>
-      <c r="N67" s="0" t="s">
-        <v>579</v>
-      </c>
-      <c r="O67" s="0" t="s">
-        <v>579</v>
-      </c>
-      <c r="P67" s="0" t="s">
-        <v>579</v>
-      </c>
-      <c r="Q67" s="0" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
-        <v>580</v>
-      </c>
-      <c r="B68" s="0" t="s">
-        <v>581</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="J68" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="K68" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="L68" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="M68" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="N68" s="2" t="s">
+      <c r="F68" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="O68" s="2" t="s">
+      <c r="G68" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="P68" s="2" t="s">
+      <c r="H68" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="Q68" s="2" t="s">
+      <c r="I68" s="0" t="s">
+        <v>593</v>
+      </c>
+      <c r="J68" s="0" t="s">
+        <v>593</v>
+      </c>
+      <c r="K68" s="0" t="s">
+        <v>593</v>
+      </c>
+      <c r="L68" s="0" t="s">
+        <v>593</v>
+      </c>
+      <c r="M68" s="0" t="s">
+        <v>593</v>
+      </c>
+      <c r="N68" s="0" t="s">
+        <v>593</v>
+      </c>
+      <c r="O68" s="0" t="s">
+        <v>593</v>
+      </c>
+      <c r="P68" s="0" t="s">
+        <v>593</v>
+      </c>
+      <c r="Q68" s="0" t="s">
         <v>593</v>
       </c>
     </row>
@@ -8060,1161 +8126,1161 @@
         <v>594</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>100</v>
+        <v>595</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="L69" s="0" t="s">
         <v>601</v>
       </c>
-      <c r="M69" s="0" t="s">
+      <c r="L69" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="N69" s="0" t="s">
+      <c r="M69" s="2" t="s">
         <v>603</v>
       </c>
+      <c r="N69" s="2" t="s">
+        <v>604</v>
+      </c>
       <c r="O69" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="Q69" s="2" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B70" s="0" t="s">
         <v>100</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L70" s="0" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M70" s="0" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N70" s="0" t="s">
-        <v>616</v>
-      </c>
-      <c r="O70" s="0" t="s">
         <v>617</v>
       </c>
-      <c r="P70" s="0" t="s">
+      <c r="O70" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="Q70" s="0" t="s">
+      <c r="P70" s="2" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="71" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q70" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="G71" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="H71" s="2" t="s">
+      <c r="D71" s="2" t="s">
         <v>623</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="L71" s="0" t="s">
+        <v>628</v>
+      </c>
+      <c r="M71" s="0" t="s">
+        <v>629</v>
+      </c>
+      <c r="N71" s="0" t="s">
+        <v>630</v>
+      </c>
+      <c r="O71" s="0" t="s">
+        <v>631</v>
+      </c>
+      <c r="P71" s="0" t="s">
+        <v>632</v>
+      </c>
+      <c r="Q71" s="0" t="s">
+        <v>633</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>624</v>
+        <v>634</v>
       </c>
       <c r="B72" s="0" t="s">
         <v>18</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>625</v>
+        <v>635</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>626</v>
+        <v>636</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="I72" s="0" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="0" t="s">
+        <v>638</v>
+      </c>
+      <c r="B73" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="I73" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="J72" s="0" t="s">
+      <c r="J73" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="K72" s="0" t="s">
+      <c r="K73" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="L72" s="0" t="s">
+      <c r="L73" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="M72" s="0" t="s">
+      <c r="M73" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="N72" s="0" t="s">
+      <c r="N73" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="O72" s="0" t="s">
+      <c r="O73" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="P72" s="0" t="s">
+      <c r="P73" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="Q72" s="0" t="s">
+      <c r="Q73" s="0" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
-        <v>628</v>
-      </c>
-      <c r="B73" s="0" t="s">
-        <v>629</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="I73" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="J73" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="K73" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="L73" s="0" t="s">
-        <v>636</v>
-      </c>
-      <c r="M73" s="0" t="s">
-        <v>637</v>
-      </c>
-      <c r="N73" s="0" t="s">
-        <v>638</v>
-      </c>
-      <c r="O73" s="0" t="s">
-        <v>639</v>
-      </c>
-      <c r="P73" s="0" t="s">
-        <v>640</v>
-      </c>
-      <c r="Q73" s="0" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
         <v>642</v>
       </c>
       <c r="B74" s="0" t="s">
+        <v>643</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="L74" s="0" t="s">
+        <v>650</v>
+      </c>
+      <c r="M74" s="0" t="s">
+        <v>651</v>
+      </c>
+      <c r="N74" s="0" t="s">
+        <v>652</v>
+      </c>
+      <c r="O74" s="0" t="s">
+        <v>653</v>
+      </c>
+      <c r="P74" s="0" t="s">
+        <v>654</v>
+      </c>
+      <c r="Q74" s="0" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="0" t="s">
+        <v>656</v>
+      </c>
+      <c r="B75" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
-        <v>646</v>
-      </c>
-      <c r="B75" s="0" t="s">
+      <c r="C75" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="0" t="s">
+        <v>660</v>
+      </c>
+      <c r="B76" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
-        <v>650</v>
-      </c>
-      <c r="B76" s="0" t="s">
-        <v>18</v>
-      </c>
       <c r="C76" s="2" t="s">
-        <v>651</v>
+        <v>661</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>652</v>
+        <v>662</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>654</v>
+        <v>664</v>
       </c>
       <c r="B77" s="0" t="s">
         <v>18</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>656</v>
+        <v>666</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>658</v>
+        <v>668</v>
       </c>
       <c r="B78" s="0" t="s">
         <v>18</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>659</v>
+        <v>669</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>670</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="I78" s="0" t="s">
-        <v>661</v>
-      </c>
-      <c r="K78" s="0" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>663</v>
+        <v>672</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>664</v>
+        <v>18</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>668</v>
-      </c>
-      <c r="J79" s="0" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="K79" s="0" t="s">
-        <v>670</v>
-      </c>
-      <c r="L79" s="0" t="s">
-        <v>671</v>
-      </c>
-      <c r="M79" s="0" t="s">
-        <v>672</v>
-      </c>
-      <c r="N79" s="0" t="s">
-        <v>673</v>
-      </c>
-      <c r="O79" s="0" t="s">
-        <v>674</v>
-      </c>
-      <c r="P79" s="0" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q79" s="0" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
         <v>677</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>18</v>
+        <v>678</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>678</v>
+        <v>679</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>680</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>680</v>
+        <v>682</v>
+      </c>
+      <c r="J80" s="0" t="s">
+        <v>683</v>
       </c>
       <c r="K80" s="0" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>684</v>
+      </c>
+      <c r="L80" s="0" t="s">
+        <v>685</v>
+      </c>
+      <c r="M80" s="0" t="s">
+        <v>686</v>
+      </c>
+      <c r="N80" s="0" t="s">
+        <v>687</v>
+      </c>
+      <c r="O80" s="0" t="s">
+        <v>688</v>
+      </c>
+      <c r="P80" s="0" t="s">
+        <v>689</v>
+      </c>
+      <c r="Q80" s="0" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>682</v>
+        <v>691</v>
       </c>
       <c r="B81" s="0" t="s">
         <v>18</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>683</v>
+        <v>692</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>684</v>
+        <v>693</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>685</v>
+        <v>694</v>
       </c>
       <c r="K81" s="0" t="s">
-        <v>686</v>
-      </c>
-      <c r="L81" s="0" t="s">
-        <v>687</v>
-      </c>
-      <c r="N81" s="0" t="s">
-        <v>688</v>
-      </c>
-      <c r="O81" s="0" t="s">
-        <v>689</v>
-      </c>
-      <c r="P81" s="0" t="s">
-        <v>690</v>
-      </c>
-      <c r="Q81" s="0" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>693</v>
+        <v>18</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="K82" s="0" t="s">
-        <v>686</v>
+        <v>700</v>
       </c>
       <c r="L82" s="0" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="N82" s="0" t="s">
-        <v>699</v>
-      </c>
-      <c r="O82" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="O82" s="0" t="s">
+        <v>703</v>
+      </c>
+      <c r="P82" s="0" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q82" s="0" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="0" t="s">
+        <v>706</v>
+      </c>
+      <c r="B83" s="0" t="s">
+        <v>707</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="I83" s="0" t="s">
+        <v>711</v>
+      </c>
+      <c r="K83" s="0" t="s">
         <v>700</v>
       </c>
-      <c r="P82" s="0" t="s">
-        <v>690</v>
-      </c>
-      <c r="Q82" s="2" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
-        <v>702</v>
-      </c>
-      <c r="B83" s="0" t="s">
+      <c r="L83" s="0" t="s">
+        <v>712</v>
+      </c>
+      <c r="N83" s="0" t="s">
+        <v>713</v>
+      </c>
+      <c r="O83" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="P83" s="0" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q83" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="0" t="s">
+        <v>716</v>
+      </c>
+      <c r="B84" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="L83" s="0" t="s">
-        <v>703</v>
-      </c>
-      <c r="M83" s="0" t="s">
-        <v>704</v>
-      </c>
-      <c r="N83" s="0" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
-        <v>706</v>
-      </c>
-      <c r="B84" s="0" t="s">
+      <c r="L84" s="0" t="s">
+        <v>717</v>
+      </c>
+      <c r="M84" s="0" t="s">
+        <v>718</v>
+      </c>
+      <c r="N84" s="0" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="0" t="s">
+        <v>720</v>
+      </c>
+      <c r="B85" s="0" t="s">
         <v>243</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C85" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D84" s="2" t="s">
+      <c r="D85" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="E84" s="2" t="s">
+      <c r="E85" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="I84" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="J84" s="0" t="s">
-        <v>708</v>
-      </c>
-      <c r="K84" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="L84" s="0" t="s">
-        <v>710</v>
-      </c>
-      <c r="M84" s="0" t="s">
-        <v>711</v>
-      </c>
-      <c r="N84" s="0" t="s">
-        <v>712</v>
-      </c>
-      <c r="O84" s="0" t="s">
-        <v>713</v>
-      </c>
-      <c r="P84" s="0" t="s">
-        <v>714</v>
-      </c>
-      <c r="Q84" s="0" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
-        <v>716</v>
-      </c>
-      <c r="B85" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C85" s="0" t="s">
-        <v>717</v>
-      </c>
-      <c r="D85" s="0" t="s">
-        <v>718</v>
-      </c>
-      <c r="E85" s="0" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I85" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="J85" s="0" t="s">
+        <v>722</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="L85" s="0" t="s">
+        <v>724</v>
+      </c>
+      <c r="M85" s="0" t="s">
+        <v>725</v>
+      </c>
+      <c r="N85" s="0" t="s">
+        <v>726</v>
+      </c>
+      <c r="O85" s="0" t="s">
+        <v>727</v>
+      </c>
+      <c r="P85" s="0" t="s">
+        <v>728</v>
+      </c>
+      <c r="Q85" s="0" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>720</v>
+        <v>730</v>
       </c>
       <c r="B86" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C86" s="0" t="s">
+        <v>731</v>
+      </c>
+      <c r="D86" s="0" t="s">
+        <v>732</v>
+      </c>
+      <c r="E86" s="0" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>724</v>
+        <v>734</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>146</v>
+        <v>18</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>725</v>
+        <v>735</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>726</v>
+        <v>736</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="L87" s="0" t="s">
-        <v>728</v>
-      </c>
-      <c r="M87" s="0" t="s">
-        <v>729</v>
-      </c>
-      <c r="N87" s="0" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="B88" s="0" t="s">
         <v>146</v>
       </c>
-      <c r="C88" s="0" t="s">
-        <v>732</v>
-      </c>
-      <c r="D88" s="0" t="s">
-        <v>733</v>
-      </c>
-      <c r="E88" s="0" t="s">
-        <v>734</v>
+      <c r="C88" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>741</v>
       </c>
       <c r="L88" s="0" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="M88" s="0" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="N88" s="0" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>146</v>
+      </c>
+      <c r="C89" s="0" t="s">
+        <v>746</v>
+      </c>
+      <c r="D89" s="0" t="s">
+        <v>747</v>
+      </c>
+      <c r="E89" s="0" t="s">
+        <v>748</v>
+      </c>
+      <c r="L89" s="0" t="s">
+        <v>749</v>
+      </c>
+      <c r="M89" s="0" t="s">
+        <v>750</v>
+      </c>
+      <c r="N89" s="0" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>741</v>
+        <v>752</v>
       </c>
       <c r="B90" s="0" t="s">
         <v>18</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>742</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>743</v>
+        <v>753</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="I90" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="K90" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="L90" s="0" t="s">
-        <v>425</v>
-      </c>
-      <c r="N90" s="0" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="B91" s="0" t="s">
         <v>18</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="J91" s="2" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="L91" s="0" t="s">
-        <v>754</v>
-      </c>
-      <c r="M91" s="0" t="s">
-        <v>755</v>
+        <v>439</v>
       </c>
       <c r="N91" s="0" t="s">
-        <v>756</v>
-      </c>
-      <c r="O91" s="0" t="s">
-        <v>757</v>
-      </c>
-      <c r="P91" s="0" t="s">
-        <v>758</v>
-      </c>
-      <c r="Q91" s="0" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B92" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="L92" s="0" t="s">
+        <v>768</v>
+      </c>
+      <c r="M92" s="0" t="s">
+        <v>769</v>
+      </c>
+      <c r="N92" s="0" t="s">
+        <v>770</v>
+      </c>
+      <c r="O92" s="0" t="s">
+        <v>771</v>
+      </c>
+      <c r="P92" s="0" t="s">
+        <v>772</v>
+      </c>
+      <c r="Q92" s="0" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="0" t="s">
+        <v>774</v>
+      </c>
+      <c r="B93" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="C92" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
-        <v>764</v>
-      </c>
-      <c r="B93" s="0" t="s">
+      <c r="C93" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="0" t="s">
+        <v>778</v>
+      </c>
+      <c r="B94" s="0" t="s">
         <v>358</v>
       </c>
-      <c r="C93" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="L93" s="0" t="s">
-        <v>768</v>
-      </c>
-      <c r="M93" s="0" t="s">
-        <v>769</v>
-      </c>
-      <c r="N93" s="0" t="s">
-        <v>770</v>
-      </c>
-      <c r="O93" s="0" t="s">
-        <v>771</v>
-      </c>
-      <c r="P93" s="0" t="s">
-        <v>772</v>
-      </c>
-      <c r="Q93" s="0" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="s">
-        <v>774</v>
-      </c>
-      <c r="B94" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L94" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="M94" s="2" t="s">
-        <v>776</v>
-      </c>
-      <c r="N94" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="O94" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="P94" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="Q94" s="2" t="s">
+      <c r="C94" s="2" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="95" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D94" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="L94" s="0" t="s">
+        <v>782</v>
+      </c>
+      <c r="M94" s="0" t="s">
+        <v>783</v>
+      </c>
+      <c r="N94" s="0" t="s">
+        <v>784</v>
+      </c>
+      <c r="O94" s="0" t="s">
+        <v>785</v>
+      </c>
+      <c r="P94" s="0" t="s">
+        <v>786</v>
+      </c>
+      <c r="Q94" s="0" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="B95" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="F95" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="I95" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="J95" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="K95" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="L95" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="M95" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="N95" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="O95" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="P95" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q95" s="0" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L95" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="M95" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="N95" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="O95" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="P95" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="Q95" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>784</v>
+        <v>794</v>
       </c>
       <c r="B96" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C96" s="0" t="s">
-        <v>785</v>
-      </c>
-      <c r="D96" s="0" t="s">
-        <v>786</v>
-      </c>
-      <c r="E96" s="0" t="s">
-        <v>787</v>
-      </c>
-      <c r="F96" s="0" t="s">
-        <v>788</v>
-      </c>
-      <c r="G96" s="0" t="s">
-        <v>789</v>
-      </c>
-      <c r="H96" s="0" t="s">
-        <v>790</v>
+      <c r="F96" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="I96" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="J96" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="K96" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="L96" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="M96" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="N96" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="O96" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="P96" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q96" s="0" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="B97" s="0" t="s">
         <v>18</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>785</v>
+        <v>799</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>787</v>
+        <v>801</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>793</v>
+        <v>802</v>
       </c>
       <c r="G97" s="0" t="s">
-        <v>794</v>
+        <v>803</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>795</v>
+        <v>804</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>796</v>
+        <v>805</v>
       </c>
       <c r="B98" s="0" t="s">
         <v>18</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="E98" s="0" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F98" s="0" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>804</v>
-      </c>
-      <c r="I99" s="0" t="s">
-        <v>805</v>
-      </c>
-      <c r="J99" s="0" t="s">
-        <v>806</v>
-      </c>
-      <c r="K99" s="0" t="s">
-        <v>807</v>
-      </c>
-      <c r="L99" s="0" t="s">
-        <v>808</v>
-      </c>
-      <c r="M99" s="0" t="s">
-        <v>809</v>
-      </c>
-      <c r="N99" s="0" t="s">
-        <v>810</v>
-      </c>
-      <c r="O99" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C99" s="0" t="s">
         <v>811</v>
       </c>
-      <c r="P99" s="0" t="s">
+      <c r="D99" s="0" t="s">
         <v>812</v>
       </c>
-      <c r="Q99" s="0" t="s">
+      <c r="E99" s="0" t="s">
         <v>813</v>
+      </c>
+      <c r="F99" s="0" t="s">
+        <v>814</v>
+      </c>
+      <c r="G99" s="0" t="s">
+        <v>815</v>
+      </c>
+      <c r="H99" s="0" t="s">
+        <v>816</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>248</v>
+        <v>818</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="J100" s="0" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="K100" s="0" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="L100" s="0" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="M100" s="0" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="N100" s="0" t="s">
-        <v>820</v>
+        <v>824</v>
+      </c>
+      <c r="O100" s="0" t="s">
+        <v>825</v>
+      </c>
+      <c r="P100" s="0" t="s">
+        <v>826</v>
+      </c>
+      <c r="Q100" s="0" t="s">
+        <v>827</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="B101" s="0" t="s">
         <v>248</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>815</v>
+        <v>829</v>
       </c>
       <c r="J101" s="0" t="s">
-        <v>816</v>
+        <v>830</v>
       </c>
       <c r="K101" s="0" t="s">
-        <v>817</v>
+        <v>831</v>
       </c>
       <c r="L101" s="0" t="s">
-        <v>822</v>
+        <v>832</v>
       </c>
       <c r="M101" s="0" t="s">
-        <v>823</v>
+        <v>833</v>
       </c>
       <c r="N101" s="0" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>825</v>
+        <v>835</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>828</v>
+        <v>248</v>
+      </c>
+      <c r="I102" s="0" t="s">
+        <v>829</v>
+      </c>
+      <c r="J102" s="0" t="s">
+        <v>830</v>
+      </c>
+      <c r="K102" s="0" t="s">
+        <v>831</v>
+      </c>
+      <c r="L102" s="0" t="s">
+        <v>836</v>
+      </c>
+      <c r="M102" s="0" t="s">
+        <v>837</v>
+      </c>
+      <c r="N102" s="0" t="s">
+        <v>838</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>829</v>
+        <v>839</v>
       </c>
       <c r="B103" s="0" t="s">
         <v>18</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>830</v>
+        <v>840</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>831</v>
+        <v>841</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>833</v>
+        <v>843</v>
       </c>
       <c r="B104" s="0" t="s">
         <v>18</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>834</v>
+        <v>844</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>835</v>
+        <v>845</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>836</v>
-      </c>
-      <c r="F104" s="0" t="s">
-        <v>837</v>
-      </c>
-      <c r="G104" s="0" t="s">
-        <v>838</v>
-      </c>
-      <c r="H104" s="0" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="B105" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="F105" s="0" t="s">
+        <v>851</v>
+      </c>
+      <c r="G105" s="0" t="s">
+        <v>852</v>
+      </c>
+      <c r="H105" s="0" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="0" t="s">
+        <v>854</v>
+      </c>
+      <c r="B106" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="C105" s="2" t="s">
-        <v>841</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>842</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>843</v>
-      </c>
-      <c r="I105" s="2" t="s">
-        <v>844</v>
-      </c>
-      <c r="J105" s="2" t="s">
-        <v>845</v>
-      </c>
-      <c r="K105" s="2" t="s">
-        <v>846</v>
-      </c>
-      <c r="L105" s="0" t="s">
-        <v>847</v>
-      </c>
-      <c r="M105" s="0" t="s">
-        <v>848</v>
-      </c>
-      <c r="N105" s="0" t="s">
-        <v>849</v>
-      </c>
-      <c r="O105" s="0" t="s">
-        <v>850</v>
-      </c>
-      <c r="P105" s="0" t="s">
-        <v>851</v>
-      </c>
-      <c r="Q105" s="0" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="0" t="s">
-        <v>853</v>
-      </c>
-      <c r="B106" s="0" t="s">
+      <c r="C106" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="J106" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="L106" s="0" t="s">
+        <v>861</v>
+      </c>
+      <c r="M106" s="0" t="s">
+        <v>862</v>
+      </c>
+      <c r="N106" s="0" t="s">
+        <v>863</v>
+      </c>
+      <c r="O106" s="0" t="s">
+        <v>864</v>
+      </c>
+      <c r="P106" s="0" t="s">
+        <v>865</v>
+      </c>
+      <c r="Q106" s="0" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="0" t="s">
+        <v>867</v>
+      </c>
+      <c r="B107" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C106" s="2" t="s">
-        <v>854</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>855</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="0" t="s">
-        <v>857</v>
-      </c>
-      <c r="B107" s="0" t="s">
-        <v>664</v>
-      </c>
       <c r="C107" s="2" t="s">
-        <v>858</v>
+        <v>868</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>859</v>
+        <v>869</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>860</v>
+        <v>870</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>861</v>
+        <v>871</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>862</v>
+        <v>678</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>863</v>
+        <v>872</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>864</v>
+        <v>873</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>866</v>
+        <v>875</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>867</v>
+        <v>876</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>868</v>
+        <v>880</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>693</v>
-      </c>
-      <c r="L110" s="0" t="s">
-        <v>869</v>
-      </c>
-      <c r="M110" s="0" t="s">
-        <v>870</v>
-      </c>
-      <c r="N110" s="0" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
-        <v>872</v>
+        <v>882</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>873</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>874</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>875</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>876</v>
-      </c>
-      <c r="I111" s="2" t="s">
-        <v>877</v>
-      </c>
-      <c r="J111" s="2" t="s">
-        <v>878</v>
-      </c>
-      <c r="K111" s="2" t="s">
-        <v>879</v>
-      </c>
-      <c r="L111" s="2" t="s">
-        <v>880</v>
-      </c>
-      <c r="M111" s="2" t="s">
-        <v>881</v>
-      </c>
-      <c r="N111" s="2" t="s">
-        <v>882</v>
-      </c>
-      <c r="O111" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="L111" s="0" t="s">
         <v>883</v>
       </c>
-      <c r="P111" s="2" t="s">
+      <c r="M111" s="0" t="s">
         <v>884</v>
       </c>
-      <c r="Q111" s="2" t="s">
+      <c r="N111" s="0" t="s">
         <v>885</v>
       </c>
     </row>
@@ -9243,13 +9309,13 @@
       <c r="K112" s="2" t="s">
         <v>893</v>
       </c>
-      <c r="L112" s="0" t="s">
+      <c r="L112" s="2" t="s">
         <v>894</v>
       </c>
-      <c r="M112" s="0" t="s">
+      <c r="M112" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="N112" s="0" t="s">
+      <c r="N112" s="2" t="s">
         <v>896</v>
       </c>
       <c r="O112" s="2" t="s">
@@ -9262,100 +9328,100 @@
         <v>899</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
         <v>900</v>
       </c>
       <c r="B113" s="0" t="s">
+        <v>901</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="J113" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="L113" s="0" t="s">
+        <v>908</v>
+      </c>
+      <c r="M113" s="0" t="s">
+        <v>909</v>
+      </c>
+      <c r="N113" s="0" t="s">
+        <v>910</v>
+      </c>
+      <c r="O113" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="P113" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="Q113" s="2" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="0" t="s">
+        <v>914</v>
+      </c>
+      <c r="B114" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="C113" s="2" t="s">
-        <v>901</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>902</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>903</v>
-      </c>
-      <c r="I113" s="2" t="s">
-        <v>904</v>
-      </c>
-      <c r="J113" s="2" t="s">
-        <v>905</v>
-      </c>
-      <c r="K113" s="2" t="s">
-        <v>906</v>
-      </c>
-      <c r="L113" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="M113" s="2" t="s">
-        <v>776</v>
-      </c>
-      <c r="N113" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="O113" s="0" t="s">
-        <v>907</v>
-      </c>
-      <c r="P113" s="0" t="s">
-        <v>908</v>
-      </c>
-      <c r="Q113" s="0" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="0" t="s">
-        <v>910</v>
-      </c>
-      <c r="B114" s="0" t="s">
+      <c r="C114" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="K114" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="L114" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="M114" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="N114" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="O114" s="0" t="s">
+        <v>921</v>
+      </c>
+      <c r="P114" s="0" t="s">
+        <v>922</v>
+      </c>
+      <c r="Q114" s="0" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="0" t="s">
+        <v>924</v>
+      </c>
+      <c r="B115" s="0" t="s">
         <v>43</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>911</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>912</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>913</v>
-      </c>
-      <c r="I114" s="2" t="s">
-        <v>914</v>
-      </c>
-      <c r="J114" s="2" t="s">
-        <v>915</v>
-      </c>
-      <c r="K114" s="2" t="s">
-        <v>916</v>
-      </c>
-      <c r="L114" s="0" t="s">
-        <v>917</v>
-      </c>
-      <c r="M114" s="0" t="s">
-        <v>918</v>
-      </c>
-      <c r="N114" s="0" t="s">
-        <v>919</v>
-      </c>
-      <c r="O114" s="2" t="s">
-        <v>920</v>
-      </c>
-      <c r="P114" s="2" t="s">
-        <v>921</v>
-      </c>
-      <c r="Q114" s="2" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="0" t="s">
-        <v>923</v>
-      </c>
-      <c r="B115" s="0" t="s">
-        <v>924</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>925</v>
@@ -9366,286 +9432,286 @@
       <c r="E115" s="2" t="s">
         <v>927</v>
       </c>
-      <c r="I115" s="0" t="s">
+      <c r="I115" s="2" t="s">
         <v>928</v>
       </c>
-      <c r="J115" s="0" t="s">
+      <c r="J115" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="K115" s="0" t="s">
+      <c r="K115" s="2" t="s">
         <v>930</v>
       </c>
       <c r="L115" s="0" t="s">
         <v>931</v>
       </c>
-      <c r="M115" s="2" t="s">
+      <c r="M115" s="0" t="s">
         <v>932</v>
       </c>
       <c r="N115" s="0" t="s">
         <v>933</v>
       </c>
-      <c r="O115" s="0" t="s">
+      <c r="O115" s="2" t="s">
         <v>934</v>
       </c>
-      <c r="P115" s="0" t="s">
+      <c r="P115" s="2" t="s">
         <v>935</v>
       </c>
-      <c r="Q115" s="0" t="s">
+      <c r="Q115" s="2" t="s">
         <v>936</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
         <v>937</v>
       </c>
       <c r="B116" s="0" t="s">
         <v>938</v>
       </c>
-      <c r="I116" s="2" t="s">
+      <c r="C116" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="J116" s="2" t="s">
+      <c r="D116" s="2" t="s">
         <v>940</v>
       </c>
-      <c r="K116" s="2" t="s">
+      <c r="E116" s="2" t="s">
         <v>941</v>
       </c>
+      <c r="I116" s="0" t="s">
+        <v>942</v>
+      </c>
+      <c r="J116" s="0" t="s">
+        <v>943</v>
+      </c>
+      <c r="K116" s="0" t="s">
+        <v>944</v>
+      </c>
       <c r="L116" s="0" t="s">
-        <v>942</v>
-      </c>
-      <c r="M116" s="0" t="s">
-        <v>943</v>
+        <v>945</v>
+      </c>
+      <c r="M116" s="2" t="s">
+        <v>946</v>
       </c>
       <c r="N116" s="0" t="s">
-        <v>944</v>
-      </c>
-      <c r="O116" s="2" t="s">
-        <v>945</v>
-      </c>
-      <c r="P116" s="2" t="s">
-        <v>946</v>
-      </c>
-      <c r="Q116" s="2" t="s">
         <v>947</v>
+      </c>
+      <c r="O116" s="0" t="s">
+        <v>948</v>
+      </c>
+      <c r="P116" s="0" t="s">
+        <v>949</v>
+      </c>
+      <c r="Q116" s="0" t="s">
+        <v>950</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>938</v>
+        <v>952</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="L117" s="0" t="s">
+        <v>956</v>
+      </c>
+      <c r="M117" s="0" t="s">
+        <v>957</v>
+      </c>
+      <c r="N117" s="0" t="s">
+        <v>958</v>
+      </c>
+      <c r="O117" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="P117" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="Q117" s="2" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="0" t="s">
+        <v>962</v>
+      </c>
+      <c r="B118" s="0" t="s">
         <v>952</v>
       </c>
-      <c r="M117" s="0" t="s">
-        <v>953</v>
-      </c>
-      <c r="N117" s="0" t="s">
-        <v>954</v>
-      </c>
-      <c r="O117" s="2" t="s">
-        <v>955</v>
-      </c>
-      <c r="P117" s="2" t="s">
-        <v>956</v>
-      </c>
-      <c r="Q117" s="2" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="0" t="s">
-        <v>958</v>
-      </c>
-      <c r="B118" s="0" t="s">
-        <v>924</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>959</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>960</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>961</v>
-      </c>
-      <c r="I118" s="0" t="s">
-        <v>962</v>
-      </c>
-      <c r="J118" s="0" t="s">
+      <c r="I118" s="2" t="s">
         <v>963</v>
       </c>
-      <c r="K118" s="0" t="s">
+      <c r="J118" s="2" t="s">
         <v>964</v>
       </c>
+      <c r="K118" s="2" t="s">
+        <v>965</v>
+      </c>
       <c r="L118" s="0" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="M118" s="0" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="N118" s="0" t="s">
-        <v>967</v>
-      </c>
-      <c r="O118" s="0" t="s">
         <v>968</v>
       </c>
-      <c r="P118" s="0" t="s">
+      <c r="O118" s="2" t="s">
         <v>969</v>
       </c>
-      <c r="Q118" s="0" t="s">
+      <c r="P118" s="2" t="s">
         <v>970</v>
+      </c>
+      <c r="Q118" s="2" t="s">
+        <v>971</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>243</v>
+        <v>938</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>974</v>
-      </c>
-      <c r="I119" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="J119" s="2" t="s">
+      <c r="I119" s="0" t="s">
         <v>976</v>
       </c>
-      <c r="K119" s="2" t="s">
+      <c r="J119" s="0" t="s">
         <v>977</v>
       </c>
+      <c r="K119" s="0" t="s">
+        <v>978</v>
+      </c>
       <c r="L119" s="0" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="M119" s="0" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="N119" s="0" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="O119" s="0" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="P119" s="0" t="s">
-        <v>969</v>
+        <v>983</v>
       </c>
       <c r="Q119" s="0" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>432</v>
+        <v>243</v>
       </c>
       <c r="C120" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="J120" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="K120" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="L120" s="0" t="s">
+        <v>992</v>
+      </c>
+      <c r="M120" s="0" t="s">
+        <v>993</v>
+      </c>
+      <c r="N120" s="0" t="s">
+        <v>994</v>
+      </c>
+      <c r="O120" s="0" t="s">
+        <v>995</v>
+      </c>
+      <c r="P120" s="0" t="s">
         <v>983</v>
       </c>
-      <c r="D120" s="2" t="s">
+      <c r="Q120" s="0" t="s">
         <v>984</v>
       </c>
-      <c r="E120" s="2" t="s">
-        <v>985</v>
-      </c>
-      <c r="I120" s="0" t="s">
-        <v>986</v>
-      </c>
-      <c r="J120" s="0" t="s">
-        <v>987</v>
-      </c>
-      <c r="K120" s="0" t="s">
-        <v>988</v>
-      </c>
-      <c r="L120" s="0" t="s">
-        <v>989</v>
-      </c>
-      <c r="M120" s="0" t="s">
-        <v>990</v>
-      </c>
-      <c r="N120" s="0" t="s">
-        <v>991</v>
-      </c>
-      <c r="O120" s="0" t="s">
-        <v>992</v>
-      </c>
-      <c r="P120" s="0" t="s">
-        <v>993</v>
-      </c>
-      <c r="Q120" s="0" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="121" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B121" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="I121" s="0" t="s">
+        <v>1000</v>
+      </c>
+      <c r="J121" s="0" t="s">
+        <v>1001</v>
+      </c>
+      <c r="K121" s="0" t="s">
+        <v>1002</v>
+      </c>
+      <c r="L121" s="0" t="s">
+        <v>1003</v>
+      </c>
+      <c r="M121" s="0" t="s">
+        <v>1004</v>
+      </c>
+      <c r="N121" s="0" t="s">
+        <v>1005</v>
+      </c>
+      <c r="O121" s="0" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P121" s="0" t="s">
+        <v>1007</v>
+      </c>
+      <c r="Q121" s="0" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="0" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B122" s="0" t="s">
         <v>43</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>996</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>997</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>998</v>
-      </c>
-      <c r="I121" s="0" t="s">
-        <v>999</v>
-      </c>
-      <c r="J121" s="0" t="s">
-        <v>1000</v>
-      </c>
-      <c r="K121" s="0" t="s">
-        <v>1001</v>
-      </c>
-      <c r="L121" s="0" t="s">
-        <v>1002</v>
-      </c>
-      <c r="M121" s="0" t="s">
-        <v>1003</v>
-      </c>
-      <c r="N121" s="0" t="s">
-        <v>1004</v>
-      </c>
-      <c r="O121" s="0" t="s">
-        <v>1005</v>
-      </c>
-      <c r="P121" s="0" t="s">
-        <v>1006</v>
-      </c>
-      <c r="Q121" s="0" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="0" t="s">
-        <v>1008</v>
-      </c>
-      <c r="B122" s="0" t="s">
-        <v>1009</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>1010</v>
@@ -9656,250 +9722,250 @@
       <c r="E122" s="2" t="s">
         <v>1012</v>
       </c>
-      <c r="I122" s="2" t="s">
+      <c r="I122" s="0" t="s">
         <v>1013</v>
       </c>
-      <c r="J122" s="2" t="s">
+      <c r="J122" s="0" t="s">
         <v>1014</v>
       </c>
-      <c r="K122" s="2" t="s">
+      <c r="K122" s="0" t="s">
         <v>1015</v>
       </c>
-      <c r="L122" s="2" t="s">
+      <c r="L122" s="0" t="s">
         <v>1016</v>
       </c>
-      <c r="M122" s="2" t="s">
+      <c r="M122" s="0" t="s">
         <v>1017</v>
       </c>
-      <c r="N122" s="2" t="s">
+      <c r="N122" s="0" t="s">
         <v>1018</v>
       </c>
-      <c r="O122" s="2" t="s">
+      <c r="O122" s="0" t="s">
         <v>1019</v>
       </c>
-      <c r="P122" s="2" t="s">
+      <c r="P122" s="0" t="s">
         <v>1020</v>
       </c>
-      <c r="Q122" s="2" t="s">
+      <c r="Q122" s="0" t="s">
         <v>1021</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
         <v>1022</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C123" s="0" t="s">
         <v>1023</v>
       </c>
-      <c r="D123" s="0" t="s">
+      <c r="C123" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="J123" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="K123" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="L123" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="M123" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="N123" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="O123" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="P123" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="Q123" s="2" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="0" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B124" s="0" t="s">
         <v>1023</v>
       </c>
-      <c r="E123" s="0" t="s">
+      <c r="C124" s="0" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D124" s="0" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E124" s="0" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="0" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B125" s="0" t="s">
         <v>1023</v>
       </c>
-    </row>
-    <row r="124" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="0" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B124" s="0" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C124" s="0" t="s">
+      <c r="C125" s="0" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D125" s="0" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E125" s="0" t="s">
+        <v>1037</v>
+      </c>
+      <c r="I125" s="0" t="s">
+        <v>1039</v>
+      </c>
+      <c r="J125" s="0" t="s">
+        <v>1040</v>
+      </c>
+      <c r="K125" s="0" t="s">
+        <v>1041</v>
+      </c>
+      <c r="L125" s="0" t="s">
+        <v>1042</v>
+      </c>
+      <c r="M125" s="0" t="s">
+        <v>1043</v>
+      </c>
+      <c r="N125" s="0" t="s">
+        <v>1044</v>
+      </c>
+      <c r="O125" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="P125" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="Q125" s="2" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="0" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B126" s="0" t="s">
         <v>1023</v>
       </c>
-      <c r="D124" s="0" t="s">
-        <v>1023</v>
-      </c>
-      <c r="E124" s="0" t="s">
-        <v>1023</v>
-      </c>
-      <c r="I124" s="0" t="s">
-        <v>1025</v>
-      </c>
-      <c r="J124" s="0" t="s">
-        <v>1026</v>
-      </c>
-      <c r="K124" s="0" t="s">
-        <v>1027</v>
-      </c>
-      <c r="L124" s="0" t="s">
-        <v>1028</v>
-      </c>
-      <c r="M124" s="0" t="s">
-        <v>1029</v>
-      </c>
-      <c r="N124" s="0" t="s">
-        <v>1030</v>
-      </c>
-      <c r="O124" s="2" t="s">
-        <v>1031</v>
-      </c>
-      <c r="P124" s="2" t="s">
-        <v>1032</v>
-      </c>
-      <c r="Q124" s="2" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="0" t="s">
-        <v>1034</v>
-      </c>
-      <c r="B125" s="0" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C125" s="0" t="s">
-        <v>1023</v>
-      </c>
-      <c r="D125" s="0" t="s">
-        <v>1023</v>
-      </c>
-      <c r="E125" s="0" t="s">
-        <v>1023</v>
-      </c>
-      <c r="I125" s="0" t="s">
-        <v>1035</v>
-      </c>
-      <c r="J125" s="0" t="s">
-        <v>1036</v>
-      </c>
-      <c r="K125" s="0" t="s">
+      <c r="C126" s="0" t="s">
         <v>1037</v>
       </c>
-      <c r="L125" s="0" t="s">
-        <v>1038</v>
-      </c>
-      <c r="M125" s="0" t="s">
-        <v>1039</v>
-      </c>
-      <c r="N125" s="0" t="s">
-        <v>1040</v>
-      </c>
-      <c r="O125" s="0" t="s">
-        <v>1041</v>
-      </c>
-      <c r="P125" s="0" t="s">
-        <v>1042</v>
-      </c>
-      <c r="Q125" s="0" t="s">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="0" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B126" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="C126" s="0" t="s">
-        <v>1045</v>
-      </c>
       <c r="D126" s="0" t="s">
-        <v>1046</v>
+        <v>1037</v>
       </c>
       <c r="E126" s="0" t="s">
-        <v>1047</v>
+        <v>1037</v>
+      </c>
+      <c r="I126" s="0" t="s">
+        <v>1049</v>
+      </c>
+      <c r="J126" s="0" t="s">
+        <v>1050</v>
+      </c>
+      <c r="K126" s="0" t="s">
+        <v>1051</v>
       </c>
       <c r="L126" s="0" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="M126" s="0" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="N126" s="0" t="s">
-        <v>1050</v>
-      </c>
-      <c r="O126" s="2" t="s">
-        <v>1051</v>
-      </c>
-      <c r="P126" s="2" t="s">
-        <v>1052</v>
-      </c>
-      <c r="Q126" s="2" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1054</v>
+      </c>
+      <c r="O126" s="0" t="s">
+        <v>1055</v>
+      </c>
+      <c r="P126" s="0" t="s">
+        <v>1056</v>
+      </c>
+      <c r="Q126" s="0" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="B127" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="C127" s="2" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>1056</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>1057</v>
+      <c r="C127" s="0" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D127" s="0" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E127" s="0" t="s">
+        <v>1061</v>
       </c>
       <c r="L127" s="0" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="M127" s="0" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="N127" s="0" t="s">
-        <v>1060</v>
+        <v>1064</v>
+      </c>
+      <c r="O127" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="P127" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="Q127" s="2" t="s">
+        <v>1067</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="0" t="s">
-        <v>1061</v>
+        <v>1068</v>
       </c>
       <c r="B128" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="L128" s="0" t="s">
+        <v>1072</v>
+      </c>
+      <c r="M128" s="0" t="s">
+        <v>1073</v>
+      </c>
+      <c r="N128" s="0" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="0" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B129" s="0" t="s">
         <v>43</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>1062</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>1063</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="I128" s="2" t="s">
-        <v>1065</v>
-      </c>
-      <c r="J128" s="2" t="s">
-        <v>1066</v>
-      </c>
-      <c r="K128" s="2" t="s">
-        <v>1067</v>
-      </c>
-      <c r="L128" s="2" t="s">
-        <v>1068</v>
-      </c>
-      <c r="M128" s="2" t="s">
-        <v>1069</v>
-      </c>
-      <c r="N128" s="2" t="s">
-        <v>1070</v>
-      </c>
-      <c r="O128" s="2" t="s">
-        <v>1071</v>
-      </c>
-      <c r="P128" s="2" t="s">
-        <v>1072</v>
-      </c>
-      <c r="Q128" s="2" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="0" t="s">
-        <v>1074</v>
-      </c>
-      <c r="B129" s="0" t="s">
-        <v>1075</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>1076</v>
@@ -9938,56 +10004,56 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
         <v>1088</v>
       </c>
       <c r="B130" s="0" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>1092</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="J130" s="2" t="s">
+        <v>1094</v>
+      </c>
+      <c r="K130" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="L130" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="M130" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="N130" s="2" t="s">
+        <v>1098</v>
+      </c>
+      <c r="O130" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P130" s="2" t="s">
+        <v>1100</v>
+      </c>
+      <c r="Q130" s="2" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="0" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B131" s="0" t="s">
         <v>43</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>1089</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>1090</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>1091</v>
-      </c>
-      <c r="I130" s="2" t="s">
-        <v>1092</v>
-      </c>
-      <c r="J130" s="2" t="s">
-        <v>1093</v>
-      </c>
-      <c r="K130" s="2" t="s">
-        <v>1094</v>
-      </c>
-      <c r="L130" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="M130" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="N130" s="0" t="s">
-        <v>1097</v>
-      </c>
-      <c r="O130" s="2" t="s">
-        <v>1098</v>
-      </c>
-      <c r="P130" s="2" t="s">
-        <v>1099</v>
-      </c>
-      <c r="Q130" s="2" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="0" t="s">
-        <v>1101</v>
-      </c>
-      <c r="B131" s="0" t="s">
-        <v>1102</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>1103</v>
@@ -10026,7 +10092,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="153.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
         <v>1115</v>
       </c>
@@ -10051,13 +10117,13 @@
       <c r="K132" s="2" t="s">
         <v>1122</v>
       </c>
-      <c r="L132" s="2" t="s">
+      <c r="L132" s="0" t="s">
         <v>1123</v>
       </c>
-      <c r="M132" s="2" t="s">
+      <c r="M132" s="0" t="s">
         <v>1124</v>
       </c>
-      <c r="N132" s="2" t="s">
+      <c r="N132" s="0" t="s">
         <v>1125</v>
       </c>
       <c r="O132" s="2" t="s">
@@ -10070,56 +10136,100 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="153.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
         <v>1129</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>1102</v>
+        <v>1130</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1133</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="K133" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="L133" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="M133" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="N133" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="O133" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="P133" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="Q133" s="2" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
-        <v>1133</v>
+        <v>1143</v>
       </c>
       <c r="B134" s="0" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="0" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B135" s="0" t="s">
         <v>243</v>
       </c>
-      <c r="I134" s="0" t="s">
-        <v>1134</v>
-      </c>
-      <c r="J134" s="0" t="s">
-        <v>1135</v>
-      </c>
-      <c r="K134" s="0" t="s">
-        <v>1136</v>
-      </c>
-      <c r="L134" s="0" t="s">
-        <v>1137</v>
-      </c>
-      <c r="M134" s="0" t="s">
-        <v>1138</v>
-      </c>
-      <c r="N134" s="0" t="s">
-        <v>699</v>
-      </c>
-      <c r="O134" s="0" t="s">
-        <v>1139</v>
-      </c>
-      <c r="P134" s="0" t="s">
-        <v>1140</v>
-      </c>
-      <c r="Q134" s="0" t="s">
-        <v>1141</v>
+      <c r="I135" s="0" t="s">
+        <v>1148</v>
+      </c>
+      <c r="J135" s="0" t="s">
+        <v>1149</v>
+      </c>
+      <c r="K135" s="0" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L135" s="0" t="s">
+        <v>1151</v>
+      </c>
+      <c r="M135" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="N135" s="0" t="s">
+        <v>713</v>
+      </c>
+      <c r="O135" s="0" t="s">
+        <v>1153</v>
+      </c>
+      <c r="P135" s="0" t="s">
+        <v>1154</v>
+      </c>
+      <c r="Q135" s="0" t="s">
+        <v>1155</v>
       </c>
     </row>
   </sheetData>
